--- a/debug/excel_overviews/gpt-4.1_vs_Qwen2.5-3B-Instruct/Qwen3-Next-80B-A3B-Instruct/metrics_default_vs_simple.xlsx
+++ b/debug/excel_overviews/gpt-4.1_vs_Qwen2.5-3B-Instruct/Qwen3-Next-80B-A3B-Instruct/metrics_default_vs_simple.xlsx
@@ -420,22 +420,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>0.124031007751938</v>
+        <v>0.1171875</v>
       </c>
       <c r="B2">
-        <v>0.1428571428571428</v>
+        <v>0.125</v>
       </c>
       <c r="C2">
-        <v>0.1619718309859155</v>
+        <v>0.1549295774647887</v>
       </c>
       <c r="D2">
-        <v>0.875</v>
+        <v>0.8823529411764706</v>
       </c>
       <c r="E2">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="F2">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G2">
         <v>6</v>

--- a/debug/excel_overviews/gpt-4.1_vs_Qwen2.5-3B-Instruct/Qwen3-Next-80B-A3B-Instruct/metrics_default_vs_simple.xlsx
+++ b/debug/excel_overviews/gpt-4.1_vs_Qwen2.5-3B-Instruct/Qwen3-Next-80B-A3B-Instruct/metrics_default_vs_simple.xlsx
@@ -423,22 +423,22 @@
         <v>0.1171875</v>
       </c>
       <c r="B2">
-        <v>0.125</v>
+        <v>0</v>
       </c>
       <c r="C2">
         <v>0.1549295774647887</v>
       </c>
       <c r="D2">
-        <v>0.8823529411764706</v>
+        <v>0.8888888888888888</v>
       </c>
       <c r="E2">
         <v>128</v>
       </c>
       <c r="F2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G2">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
